--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104725_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104725_W30.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4032</v>
+        <v>6.6182</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8639</v>
+        <v>5.1175</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5394</v>
+        <v>1.5007</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2963</v>
+        <v>6.2863</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3377</v>
+        <v>5.3234</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9587</v>
+        <v>0.9629</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6192</v>
+        <v>6.5958</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2025</v>
+        <v>5.1808</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4167</v>
+        <v>1.415</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3228</v>
+        <v>-0.3095</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1352</v>
+        <v>0.1426</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.458</v>
+        <v>-0.4521</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6056</v>
+        <v>-0.1626</v>
       </c>
       <c r="T2" t="n">
-        <v>2.083</v>
+        <v>0.3734</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4775</v>
+        <v>-0.5359</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4101</v>
+        <v>1.405</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5695</v>
+        <v>1.5628</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.218</v>
+        <v>5.7792</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1619</v>
+        <v>6.2665</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9439</v>
+        <v>-0.4874</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5104</v>
+        <v>2.5006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3081</v>
+        <v>0.3023</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2023</v>
+        <v>2.1983</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3659</v>
+        <v>4.3461</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9167</v>
+        <v>0.9061</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4492</v>
+        <v>3.44</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8555</v>
+        <v>-1.8455</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2469</v>
+        <v>-1.2417</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6108</v>
+        <v>0.9615</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.41</v>
+        <v>0.7219</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2008</v>
+        <v>0.2396</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6432</v>
+        <v>2.7031</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8563</v>
+        <v>3.0826</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2131</v>
+        <v>-0.3795</v>
       </c>
       <c r="G4" t="n">
-        <v>1.28</v>
+        <v>1.2814</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8566</v>
+        <v>1.8579</v>
       </c>
       <c r="I4" t="n">
         <v>-0.5765</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9016</v>
+        <v>1.8939</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5035</v>
+        <v>1.4996</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3981</v>
+        <v>0.3943</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.6125</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3531</v>
+        <v>0.3583</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4779</v>
+        <v>1.5308</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7954</v>
+        <v>1.0309</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6825</v>
+        <v>0.4999</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3405</v>
+        <v>2.2041</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3268</v>
+        <v>4.0748</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9864</v>
+        <v>-1.8707</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1145</v>
+        <v>1.1064</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2795</v>
+        <v>-1.2807</v>
       </c>
       <c r="I5" t="n">
-        <v>2.394</v>
+        <v>2.3871</v>
       </c>
       <c r="J5" t="n">
-        <v>2.599</v>
+        <v>2.578</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0991</v>
+        <v>-1.1074</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6981</v>
+        <v>3.6853</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4846</v>
+        <v>-1.4715</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1804</v>
+        <v>-0.1733</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3042</v>
+        <v>-1.2982</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.774</v>
+        <v>-0.9024</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.0887</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9096</v>
+        <v>-0.8136</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4161</v>
+        <v>0.5142</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0151</v>
+        <v>1.1267</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.599</v>
+        <v>-0.6125</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1513</v>
+        <v>-2.1471</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4343</v>
+        <v>-1.4307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.717</v>
+        <v>-0.7165</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9409</v>
+        <v>-0.945</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6679</v>
+        <v>-0.669</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.273</v>
+        <v>-0.276</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2104</v>
+        <v>-1.2022</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7664</v>
+        <v>-0.7617</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.444</v>
+        <v>-0.4405</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0457</v>
+        <v>1.1346</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8648</v>
+        <v>0.9822</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1809</v>
+        <v>0.1524</v>
       </c>
       <c r="V6" t="n">
-        <v>0.613</v>
+        <v>0.6162</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4782</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1417</v>
+        <v>0.4723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2025</v>
+        <v>0.7333</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0608</v>
+        <v>-0.261</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6532</v>
+        <v>0.6546</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5485</v>
+        <v>-0.546</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2017</v>
+        <v>1.2006</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0164</v>
+        <v>1.0077</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0594</v>
+        <v>-1.0622</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0758</v>
+        <v>2.0699</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3632</v>
+        <v>-0.3532</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5109</v>
+        <v>0.5162</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8741</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2377</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8139</v>
+        <v>-0.2744</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4238</v>
+        <v>-0.6394</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1041</v>
+        <v>0.2978</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7055</v>
+        <v>0.6119</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6014</v>
+        <v>-0.3141</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2601</v>
+        <v>0.3964</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9857</v>
+        <v>2.47</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7257</v>
+        <v>-2.0737</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0114</v>
+        <v>0.0208</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06909999999999999</v>
+        <v>2.2408</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0806</v>
+        <v>-2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2715</v>
+        <v>0.3755</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9166</v>
+        <v>0.2292</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6451</v>
+        <v>0.1463</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4544</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0902</v>
+        <v>-0.9604</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4419</v>
+        <v>0.095</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3516</v>
+        <v>-1.0554</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2707</v>
+        <v>-0.4264</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2713</v>
+        <v>-1.0656</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.542</v>
+        <v>0.6391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3982</v>
+        <v>0.2622</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4719</v>
+        <v>0.9876</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0738</v>
+        <v>-0.7255</v>
       </c>
       <c r="J9" t="n">
-        <v>0.029</v>
+        <v>-0.0132</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2466</v>
+        <v>0.0689</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2176</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3692</v>
+        <v>0.2754</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2254</v>
+        <v>0.9187</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1438</v>
+        <v>-0.6433</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2272</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9087</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5329</v>
+        <v>-0.2334</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2587</v>
+        <v>0.0858</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2743</v>
+        <v>-0.3191</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6369</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3979</v>
+        <v>-3.2464</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1153</v>
+        <v>-1.5625</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2826</v>
+        <v>-1.6839</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9532</v>
+        <v>0.585</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1217</v>
+        <v>0.1318</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8315</v>
+        <v>0.4532</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5446</v>
+        <v>0.8557</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.731</v>
+        <v>0.7067</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1864</v>
+        <v>0.1489</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4086</v>
+        <v>-0.2706</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3907</v>
+        <v>-0.5749</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0179</v>
+        <v>0.3043</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0447</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8507</v>
+        <v>-0.5144</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7012</v>
+        <v>-0.1418</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1495</v>
+        <v>-0.3725</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2507</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2507</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0894</v>
+        <v>-3.6095</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6729</v>
+        <v>-1.306</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4165</v>
+        <v>-2.3036</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5807</v>
+        <v>-1.9522</v>
       </c>
       <c r="H11" t="n">
-        <v>0.13</v>
+        <v>-1.1227</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4507</v>
+        <v>-0.8295</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8577</v>
+        <v>-0.5485</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7085</v>
+        <v>-0.7347</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1491</v>
+        <v>0.1862</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.277</v>
+        <v>-1.4037</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5786</v>
+        <v>-0.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3016</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1359</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3516</v>
+        <v>1.6386</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2587</v>
+        <v>1.5188</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.093</v>
+        <v>0.1198</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1825</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1825</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1672</v>
+        <v>-3.8277</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0568</v>
+        <v>-2.759</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1104</v>
+        <v>-1.0687</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5932</v>
+        <v>-3.5921</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8077</v>
+        <v>-0.8045</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7855</v>
+        <v>-2.7875</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8389</v>
+        <v>-1.8436</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0864</v>
+        <v>0.0862</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9253</v>
+        <v>-1.9298</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7543</v>
+        <v>-1.7485</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8941</v>
+        <v>-0.8907</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8601</v>
+        <v>-0.8578</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>0.267</v>
+        <v>0.605</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0819</v>
+        <v>0.2228</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3489</v>
+        <v>0.3823</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.133400000000001</v>
+        <v>7.478900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1473</v>
+        <v>14.3202</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.0139</v>
+        <v>-6.8416</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3957</v>
+        <v>5.381499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8983</v>
+        <v>5.888400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5025999999999997</v>
+        <v>-0.5071000000000003</v>
       </c>
       <c r="J13" t="n">
-        <v>14.053</v>
+        <v>13.9477</v>
       </c>
       <c r="K13" t="n">
-        <v>7.1759</v>
+        <v>7.115799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6.876900000000001</v>
+        <v>6.831699999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.6572</v>
+        <v>-8.566299999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2776</v>
+        <v>-1.2274</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.3795</v>
+        <v>-7.338900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-7.771561172376096e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6311</v>
+        <v>-13.6581</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6312</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8301</v>
+        <v>2.1835</v>
       </c>
       <c r="T13" t="n">
-        <v>4.198700000000001</v>
+        <v>4.5259</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3688</v>
+        <v>-2.3419</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.09199999999999986</v>
+        <v>-0.08620000000000011</v>
       </c>
       <c r="W13" t="n">
-        <v>9.527100000000001</v>
+        <v>9.5047</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.6191</v>
+        <v>-9.5909</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.04</v>
+        <v>5.3</v>
       </c>
       <c r="E14" t="n">
-        <v>4.494</v>
+        <v>4.8194</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4541</v>
+        <v>0.4806</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7015</v>
+        <v>0.6976</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5004</v>
+        <v>0.4947</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4487</v>
+        <v>0.4335</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1624</v>
+        <v>0.1509</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2863</v>
+        <v>0.2826</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2529</v>
+        <v>0.2641</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3381</v>
+        <v>0.3438</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0852</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0716</v>
+        <v>0.1974</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.025</v>
+        <v>0.3271</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0466</v>
+        <v>-0.1297</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0469</v>
+        <v>3.0392</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2976</v>
+        <v>4.2865</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8944</v>
+        <v>1.8095</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0779</v>
+        <v>1.43</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8165</v>
+        <v>0.3795</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.4486</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0301</v>
+        <v>0.17</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0386</v>
+        <v>0.2786</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3513</v>
+        <v>0.3585</v>
       </c>
       <c r="K15" t="n">
-        <v>0.127</v>
+        <v>0.1132</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2243</v>
+        <v>0.2453</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3429</v>
+        <v>0.0901</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1571</v>
+        <v>0.0568</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1857</v>
+        <v>0.0333</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5903</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8625</v>
+        <v>0.8373</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2522</v>
+        <v>0.369</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1147</v>
+        <v>0.4683</v>
       </c>
       <c r="V15" t="n">
-        <v>0.705</v>
+        <v>-0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2507</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5456</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8433</v>
+        <v>0.7846</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3284</v>
+        <v>-0.1824</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4851</v>
+        <v>0.9669</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4526</v>
+        <v>0.4705</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1743</v>
+        <v>0.4076</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2783</v>
+        <v>0.0629</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3708</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1218</v>
+        <v>0.6378</v>
       </c>
       <c r="L16" t="n">
-        <v>0.249</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0819</v>
+        <v>-0.2417</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0526</v>
+        <v>-0.2301</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0293</v>
+        <v>-0.0116</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9087</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1319</v>
+        <v>0.223</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2526</v>
+        <v>0.0858</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3845</v>
+        <v>0.1372</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3862</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
-        <v>0.705</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0913</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5996</v>
+        <v>0.6761</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1793</v>
+        <v>0.1785</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4203</v>
+        <v>0.4976</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4671</v>
+        <v>0.0142</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4065</v>
+        <v>-1.0258</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0606</v>
+        <v>1.04</v>
       </c>
       <c r="J17" t="n">
-        <v>0.714</v>
+        <v>1.3451</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6394</v>
+        <v>0.1239</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>1.2211</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2469</v>
+        <v>-1.3309</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2329</v>
+        <v>-1.1497</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.014</v>
+        <v>-0.1811</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4544</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0416</v>
+        <v>0.6423</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4419</v>
+        <v>-0.1375</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4002</v>
+        <v>0.7798</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7724</v>
+        <v>0.7025</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1594</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>0.613</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2809</v>
+        <v>0.3626</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7448</v>
+        <v>1.0178</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4639</v>
+        <v>-0.6552</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7874</v>
+        <v>2.1836</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5041</v>
+        <v>-3.8192</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2915</v>
+        <v>6.0028</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3594</v>
+        <v>3.5987</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6763</v>
+        <v>-3.0142</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3168</v>
+        <v>6.6128</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1468</v>
+        <v>-1.415</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1722</v>
+        <v>-0.805</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9746</v>
+        <v>-0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4544</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3631</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8175</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6139</v>
+        <v>-0.4553</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2029</v>
+        <v>-0.0283</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.589</v>
+        <v>-0.427</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5456</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5456</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8046</v>
+        <v>-0.2676</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4687</v>
+        <v>1.4639</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2733</v>
+        <v>-1.7315</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.157</v>
+        <v>1.9009</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3914</v>
+        <v>0.0224</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7655999999999999</v>
+        <v>1.8785</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1813</v>
+        <v>2.8858</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2186</v>
+        <v>0.1379</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>2.7479</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9757</v>
+        <v>-0.9849</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1728</v>
+        <v>-0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.8694</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2272</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6709000000000001</v>
+        <v>-0.5342</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6501</v>
+        <v>-0.0561</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0208</v>
+        <v>-0.4782</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5456</v>
+        <v>-1.6342</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5456</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0997</v>
+        <v>-0.7308</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8904</v>
+        <v>0.4306</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2092</v>
+        <v>-1.1615</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9817</v>
+        <v>-1.7816</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1728</v>
+        <v>0.5078</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8089</v>
+        <v>-2.2894</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7516</v>
+        <v>0.3533</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.672</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7516</v>
+        <v>-1.3186</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2301</v>
+        <v>-2.135</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1728</v>
+        <v>-1.1642</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0573</v>
+        <v>-0.9708</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.118</v>
+        <v>0.5955</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1388</v>
+        <v>0.8983</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0208</v>
+        <v>-0.3028</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>G. FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1381</v>
+        <v>-1.0684</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1033</v>
+        <v>-0.8918</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2415</v>
+        <v>-0.1766</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1915</v>
+        <v>-0.9813</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.8168</v>
+        <v>-0.1724</v>
       </c>
       <c r="I21" t="n">
-        <v>6.0083</v>
+        <v>-0.8089</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6188</v>
+        <v>-0.7524</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.0053</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>6.6241</v>
+        <v>-0.7524</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4273</v>
+        <v>-0.2289</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8115</v>
+        <v>-0.1724</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6158</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.635</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2719</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9665</v>
+        <v>-0.0871</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9717</v>
+        <v>-0.1394</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9948</v>
+        <v>0.0523</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5817</v>
+        <v>-1.2456</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7645</v>
+        <v>-0.0071</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3462</v>
+        <v>-1.2384</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8967</v>
+        <v>-1.1572</v>
       </c>
       <c r="H22" t="n">
-        <v>0.018</v>
+        <v>-0.3932</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8787</v>
+        <v>-0.764</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8911</v>
+        <v>-0.1836</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1383</v>
+        <v>-0.2208</v>
       </c>
       <c r="L22" t="n">
-        <v>2.7528</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9944</v>
+        <v>-0.9736</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1203</v>
+        <v>-0.1724</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8741</v>
+        <v>-0.8012</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3631</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8416</v>
+        <v>0.2287</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7635</v>
+        <v>0.1765</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0781</v>
+        <v>0.0523</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6369</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6369</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5891</v>
+        <v>-2.0307</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1254</v>
+        <v>-0.3594</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7145</v>
+        <v>-1.6714</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.53</v>
+        <v>-0.5236</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.514</v>
+        <v>-1.5085</v>
       </c>
       <c r="I23" t="n">
-        <v>0.984</v>
+        <v>0.9848</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9878</v>
+        <v>1.9853</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0864</v>
+        <v>0.0862</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9013</v>
+        <v>1.8991</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5178</v>
+        <v>-2.5089</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6004</v>
+        <v>-1.5946</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9171</v>
+        <v>0.4749</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0225</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1055</v>
+        <v>-0.073</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.613</v>
+        <v>-0.6162</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.613</v>
+        <v>-0.6162</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9925</v>
+        <v>-3.2652</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5764</v>
+        <v>-1.3733</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5689</v>
+        <v>-1.8919</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.9362</v>
+        <v>-2.7168</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2832</v>
+        <v>-0.8562</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.2195</v>
+        <v>-1.8605</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7987</v>
+        <v>-1.3567</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9588</v>
+        <v>-0.4104</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.7575</v>
+        <v>-0.9463</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.1375</v>
+        <v>-1.3601</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6756</v>
+        <v>-0.4458</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4619</v>
+        <v>-0.9143</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6816</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3631</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0447</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4215</v>
+        <v>0.0858</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5557</v>
+        <v>-0.0166</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1341</v>
+        <v>0.1024</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1825</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3419</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5859</v>
+        <v>-3.5065</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9584</v>
+        <v>0.3152</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6274</v>
+        <v>-3.8217</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.721</v>
+        <v>-3.9363</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8596</v>
+        <v>0.2842</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8614</v>
+        <v>-4.2205</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3527</v>
+        <v>-0.8133</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4087</v>
+        <v>1.951</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.944</v>
+        <v>-2.7643</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3682</v>
+        <v>-3.123</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4508</v>
+        <v>-1.6668</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9174</v>
+        <v>-1.4562</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4544</v>
+        <v>2.0487</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.228</v>
+        <v>-0.0953</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6057</v>
+        <v>0.3154</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6223</v>
+        <v>-0.4107</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0913</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.1334</v>
+        <v>-3.182</v>
       </c>
       <c r="E26" t="n">
-        <v>7.013899999999999</v>
+        <v>6.841400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.1473</v>
+        <v>-10.0236</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.3955</v>
+        <v>-5.381400000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.898200000000001</v>
+        <v>-5.888599999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5027000000000006</v>
+        <v>0.5070999999999986</v>
       </c>
       <c r="J26" t="n">
-        <v>8.657599999999999</v>
+        <v>8.566400000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2778</v>
+        <v>1.2275</v>
       </c>
       <c r="L26" t="n">
-        <v>7.379799999999999</v>
+        <v>7.338899999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-14.0528</v>
+        <v>-13.9478</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.1757</v>
+        <v>-7.115900000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.877</v>
+        <v>-6.8318</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>3.33066907387547e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6312</v>
+        <v>-13.6579</v>
       </c>
       <c r="R26" t="n">
-        <v>13.6312</v>
+        <v>13.6579</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.8301</v>
+        <v>2.113</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3688</v>
+        <v>2.3421</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.1988</v>
+        <v>-0.2290999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.09189999999999987</v>
+        <v>0.08620000000000089</v>
       </c>
       <c r="W26" t="n">
-        <v>9.6191</v>
+        <v>9.5909</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.527200000000001</v>
+        <v>-9.5045</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104725_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104725_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.5909</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104725_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.5045</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
